--- a/bloomberg/CDS_PricerSheet_v7.xlsx
+++ b/bloomberg/CDS_PricerSheet_v7.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer_NEW" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_MOVE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer_NEW" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Curve_Interface!$O$5</definedName>
@@ -33,7 +34,7 @@
     <numFmt numFmtId="175" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="176" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -217,7 +218,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -227,6 +228,11 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
@@ -321,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -647,6 +653,7 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -729,31 +736,31 @@
     <author>B-Model white paper</author>
   </authors>
   <commentList>
-    <comment ref="B11" authorId="0" shapeId="0">
+    <comment ref="B5" authorId="0" shapeId="0">
       <text>
         <t>p.6 — the recovery rate is a model parameter, conventionally 40%, not an
 observable. It sets the payout (1-R)A and feeds the credit triangle.</t>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0">
+    <comment ref="B6" authorId="0" shapeId="0">
       <text>
         <t>p.6 — coupons are standardised to 100bp / 500bp for most names, ACT/360.
 Overtype to price an off-market coupon.</t>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0">
+    <comment ref="B8" authorId="0" shapeId="0">
       <text>
         <t>p.6 — accrual dates are IMM: 3/20, 6/20, 9/20, 12/20. Payment dates roll to the
 next business day; the last accrual end date T_M does not roll.</t>
       </text>
     </comment>
-    <comment ref="B18" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
         <t>(3.4) coupons-in-survival + (3.5) accrued-on-default.
 RPV01 is the premium leg per 1bp of coupon.</t>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
+    <comment ref="B13" authorId="0" shapeId="0">
       <text>
         <t>(3.6)  Protection Leg = A(1-R) * INT_T^TM (-dp_s/dt) D(t) dt
 p.8: the timeline is cut into segments short enough to treat the forward
@@ -761,26 +768,26 @@
 accrual period. The integral is then analytic on each segment.</t>
       </text>
     </comment>
-    <comment ref="B20" authorId="0" shapeId="0">
+    <comment ref="B14" authorId="0" shapeId="0">
       <text>
         <t>(3.4)  Coupons-in-Survival = A * C * SUM delta(T_i-1,T_i) p_s(T_i) D(T_i)</t>
       </text>
     </comment>
-    <comment ref="B21" authorId="0" shapeId="0">
+    <comment ref="B15" authorId="0" shapeId="0">
       <text>
         <t>(3.3)  S = Protection Leg / (Premium Leg - Accrued Interest * D(T_s)) at C=1bp.
 p.7: the par spread is the replacement spread, quoted in bp, expressed as the
 protection leg over the premium leg net of accrued interest.</t>
       </text>
     </comment>
-    <comment ref="B24" authorId="0" shapeId="0">
+    <comment ref="B18" authorId="0" shapeId="0">
       <text>
         <t>(3.2)  Upfront = Market Value / D(T_s) + Accrued Interest.
 p.7: quoted at the settlement date T_s, typically 3 business days after pricing,
 so the market value is compounded from T to T_s. Identically 0 when C = S.</t>
       </text>
     </comment>
-    <comment ref="B26" authorId="0" shapeId="0">
+    <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t>(3.1)  Market Value = Protection Leg - Premium Leg, both discounted to the
 pricing date T.</t>
@@ -1076,11 +1083,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="230" t="inlineStr">
+        <is>
+          <t>Moving the reformed CDS_Pricer in</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="231" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="232" t="inlineStr">
+        <is>
+          <t>Move the CDS_Pricer_NEW tab only. Leave this sheet behind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="231" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="233" t="inlineStr">
+        <is>
+          <t>1.  Open both workbooks and keep both open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="233" t="inlineStr">
+        <is>
+          <t>2.  Right-click the CDS_Pricer_NEW tab &gt; Move or Copy &gt; To book: your CDS_Pricer workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="233" t="inlineStr">
+        <is>
+          <t>3.  On the moved tab: Ctrl+H, Options, Look in Formulas, Within Sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Find what:     [CDS_PricerSheet_v7.xlsx]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         Replace with:  (leave empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="233" t="inlineStr">
+        <is>
+          <t>4.  Delete the old CDS_Pricer tab, then rename this one to exactly  CDS_Pricer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="231" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="232" t="inlineStr">
+        <is>
+          <t>Modules needed: CDSStrip.bas and CDSRisk.bas. Save as .xlsm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="231" t="inlineStr">
+        <is>
+          <t>Sheets it reads: CDS_Parameters, CDS_Schedule, Curve_Interface, Hazard_Bootstrap,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="231" t="inlineStr">
+        <is>
+          <t>CDS_Quotes, CDS_Entities, Steps. All are in your workbook already.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="231" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="231" t="inlineStr">
+        <is>
+          <t>Opened on its own the tab shows #REF - expected, those sheets are not in this file.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="006A1B9A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1089,866 +1209,823 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="230" t="inlineStr">
-        <is>
-          <t>Reformed CDS_Pricer - move this tab into your workbook</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CDS_Pricer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="231" t="inlineStr">
-        <is>
-          <t>Tab is CDS_Pricer_NEW so it cannot collide. Rename it to exactly CDS_Pricer after the move.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Prices a CDS off the SOFR discount curve and the stripped hazard curve. Equations on Model_Notes.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="232" t="inlineStr">
-        <is>
-          <t>1. Open both workbooks, keep both open.   2. Right-click this tab &gt; Move or Copy &gt; To book: your CDS_Pricer workbook.</t>
+      <c r="J3" s="136" t="inlineStr">
+        <is>
+          <t>PRICING EQUATIONS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="165" t="inlineStr">
-        <is>
-          <t>3. On the moved tab: Ctrl+H, Options, Look in Formulas, Within Sheet.  Find  [CDS_PricerSheet_v7.xlsx]  Replace with nothing.</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Notional</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>CDS_Parameters!$B$9</f>
+        <v/>
+      </c>
+      <c r="J4" s="138" t="inlineStr">
+        <is>
+          <t>(3.1)  Market Value = Protection Leg - Premium Leg</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="232" t="inlineStr">
-        <is>
-          <t>4. Delete the old CDS_Pricer, rename this one CDS_Pricer.  Import CDSStrip.bas and CDSRisk.bas, save as .xlsm.</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Recovery R</t>
+        </is>
+      </c>
+      <c r="B5" s="58">
+        <f>CDS_Parameters!$B$8</f>
+        <v/>
+      </c>
+      <c r="J5" s="139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       both discounted to the pricing date T</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="231" t="inlineStr">
-        <is>
-          <t>Opened on its own this shows #REF throughout - expected, the sheets it reads are not in this file.</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Contractual coupon (bp)</t>
+        </is>
+      </c>
+      <c r="B6" s="41">
+        <f>CDS_Parameters!$B$10</f>
+        <v/>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Overtype to price an off-market coupon.</t>
+        </is>
+      </c>
+      <c r="J6" s="138" t="inlineStr">
+        <is>
+          <t>(3.2)  Upfront      = Market Value / D(T_s) + Accrued Interest</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>CDS_Pricer</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Maturity (tenor yrs)</t>
+        </is>
+      </c>
+      <c r="B7" s="41">
+        <f>IF(Steps!$B$9="",5,Steps!$B$9)</f>
+        <v/>
+      </c>
+      <c r="J7" s="138" t="inlineStr">
+        <is>
+          <t>(3.3)  Par spread S = Protection / (Premium - AI*D(T_s))   at C=1bp</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Prices a CDS off the SOFR discount curve and the stripped hazard curve. Equations on Model_Notes.</t>
-        </is>
-      </c>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Maturity date</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*(4*B7-1))</f>
+        <v/>
+      </c>
+      <c r="J8" s="137" t="n"/>
     </row>
     <row r="9">
-      <c r="J9" s="136" t="inlineStr">
-        <is>
-          <t>PRICING EQUATIONS</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>CDS_Parameters!$B$15</f>
+        <v/>
+      </c>
+      <c r="J9" s="138" t="inlineStr">
+        <is>
+          <t>O-T (1b)  MTM = +/- [ S(t_V,t_N) - S(t_0,t_N) ] * RPV01</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Notional</t>
-        </is>
-      </c>
-      <c r="B10" s="21">
-        <f>CDS_Parameters!$B$9</f>
-        <v/>
-      </c>
-      <c r="J10" s="138" t="inlineStr">
-        <is>
-          <t>(3.1)  Market Value = Protection Leg - Premium Leg</t>
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+      <c r="J10" s="139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          equivalent form, + for long protection</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Recovery R</t>
-        </is>
-      </c>
-      <c r="B11" s="58">
-        <f>CDS_Parameters!$B$8</f>
-        <v/>
-      </c>
-      <c r="J11" s="139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       both discounted to the pricing date T</t>
-        </is>
-      </c>
+      <c r="A11" s="59" t="inlineStr">
+        <is>
+          <t>RESULTS</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="J11" s="137" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Contractual coupon (bp)</t>
-        </is>
-      </c>
-      <c r="B12" s="41">
-        <f>CDS_Parameters!$B$10</f>
+          <t>RPV01 (risky annuity)</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$N$7:$N$46)</f>
         <v/>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Overtype to price an off-market coupon.</t>
+          <t>Scheduled + accrual-on-default.</t>
         </is>
       </c>
       <c r="J12" s="138" t="inlineStr">
         <is>
-          <t>(3.2)  Upfront      = Market Value / D(T_s) + Accrued Interest</t>
+          <t>Accrued Interest = A * C * D0,   D0 = accrued days / 360</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Maturity (tenor yrs)</t>
-        </is>
-      </c>
-      <c r="B13" s="41">
-        <f>IF(Steps!$B$9="",5,Steps!$B$9)</f>
-        <v/>
-      </c>
-      <c r="J13" s="138" t="inlineStr">
-        <is>
-          <t>(3.3)  Par spread S = Protection / (Premium - AI*D(T_s))   at C=1bp</t>
+          <t>Protection PV</t>
+        </is>
+      </c>
+      <c r="B13" s="44">
+        <f>B4*(1-B5)*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="J13" s="139" t="inlineStr">
+        <is>
+          <t>accrued days include the pricing date (p.7)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Maturity date</t>
-        </is>
-      </c>
-      <c r="B14" s="18">
-        <f>EDATE('Curve_Interface'!$F$7,3*(4*B7-1))</f>
-        <v/>
-      </c>
-      <c r="J14" s="137" t="n"/>
+          <t>Premium PV (@ coupon)</t>
+        </is>
+      </c>
+      <c r="B14" s="44">
+        <f>B4*(B6/10000)*B12</f>
+        <v/>
+      </c>
+      <c r="J14" s="139" t="inlineStr">
+        <is>
+          <t>T_s = T + 3 business days (p.6)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <f>CDS_Parameters!$B$15</f>
-        <v/>
-      </c>
-      <c r="J15" s="138" t="inlineStr">
-        <is>
-          <t>O-T (1b)  MTM = +/- [ S(t_V,t_N) - S(t_0,t_N) ] * RPV01</t>
-        </is>
-      </c>
+      <c r="A15" s="132" t="inlineStr">
+        <is>
+          <t>Par spread (bp)  (3.3)</t>
+        </is>
+      </c>
+      <c r="B15" s="133">
+        <f>(1-B5)*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)/(B12-CDS_Parameters!$B$26)*10000</f>
+        <v/>
+      </c>
+      <c r="C15" s="65" t="inlineStr">
+        <is>
+          <t>Protection / (RPV01 net of accrued interest x D(T_s)).</t>
+        </is>
+      </c>
+      <c r="J15" s="137" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>PV: protection buyer</t>
+        </is>
+      </c>
+      <c r="B16" s="44">
+        <f>B13-B14</f>
+        <v/>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Protection − Premium.</t>
+        </is>
+      </c>
       <c r="J16" s="139" t="inlineStr">
         <is>
-          <t xml:space="preserve">          equivalent form, + for long protection</t>
+          <t>Upfront is identically 0 when C = S. That is the check that accrued</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="59" t="inlineStr">
-        <is>
-          <t>RESULTS</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="J17" s="137" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>PV to your direction</t>
+        </is>
+      </c>
+      <c r="B17" s="44">
+        <f>IF(B9="Buy protection",B13-B14,B14-B13)</f>
+        <v/>
+      </c>
+      <c r="J17" s="139" t="inlineStr">
+        <is>
+          <t>interest enters with a + sign, which the wording alone does not settle.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>RPV01 (risky annuity)</t>
-        </is>
-      </c>
-      <c r="B18" s="17">
-        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$N$7:$N$46)</f>
-        <v/>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Scheduled + accrual-on-default.</t>
-        </is>
-      </c>
-      <c r="J18" s="138" t="inlineStr">
-        <is>
-          <t>Accrued Interest = A * C * D0,   D0 = accrued days / 360</t>
-        </is>
+          <t>Upfront (% notional)</t>
+        </is>
+      </c>
+      <c r="B18" s="60">
+        <f>B17/B4*100</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Protection PV</t>
-        </is>
-      </c>
-      <c r="B19" s="44">
-        <f>B4*(1-B5)*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
-        <v/>
-      </c>
-      <c r="J19" s="139" t="inlineStr">
-        <is>
-          <t>accrued days include the pricing date (p.7)</t>
-        </is>
+      <c r="A19" s="132" t="inlineStr">
+        <is>
+          <t>PV01  (premium leg net of AI, per 1bp)</t>
+        </is>
+      </c>
+      <c r="B19" s="120">
+        <f>B4*(B12-CDS_Parameters!$B$26)*0.0001</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Premium PV (@ coupon)</t>
-        </is>
-      </c>
-      <c r="B20" s="44">
-        <f>B4*(B6/10000)*B12</f>
-        <v/>
-      </c>
-      <c r="J20" s="139" t="inlineStr">
-        <is>
-          <t>T_s = T + 3 business days (p.6)</t>
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t>Market Value  (3.1)</t>
+        </is>
+      </c>
+      <c r="B20" s="119">
+        <f>B13-B14</f>
+        <v/>
+      </c>
+      <c r="C20" s="65" t="inlineStr">
+        <is>
+          <t>Protection leg minus premium leg, both to the pricing date.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="132" t="inlineStr">
-        <is>
-          <t>Par spread (bp)  (3.3)</t>
-        </is>
-      </c>
-      <c r="B21" s="133">
-        <f>(1-B5)*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)/(B12-CDS_Parameters!$B$26)*10000</f>
-        <v/>
-      </c>
-      <c r="C21" s="65" t="inlineStr">
-        <is>
-          <t>Protection / (RPV01 net of accrued interest x D(T_s)).</t>
-        </is>
-      </c>
-      <c r="J21" s="137" t="n"/>
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>RISK MEASURES (full revalue, curve re-stripped on each bump)</t>
+        </is>
+      </c>
+      <c r="N21" s="67" t="inlineStr">
+        <is>
+          <t>full-revalue working</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>PV: protection buyer</t>
+          <t>CS01 / Spread DV01  (+1bp)</t>
         </is>
       </c>
       <c r="B22" s="44">
-        <f>B13-B14</f>
-        <v/>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Protection − Premium.</t>
-        </is>
-      </c>
-      <c r="J22" s="139" t="inlineStr">
-        <is>
-          <t>Upfront is identically 0 when C = S. That is the check that accrued</t>
-        </is>
+        <f>IF(OR($O$22="",$O$23=""),"",$O$23-$O$22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="177" t="inlineStr">
+        <is>
+          <t>Spread DV01: revalue at +1bp on every quote, curve re-stripped (p.9).</t>
+        </is>
+      </c>
+      <c r="N22" s="126" t="inlineStr">
+        <is>
+          <t>MV base</t>
+        </is>
+      </c>
+      <c r="O22" s="229">
+        <f>IFERROR(CDS_MarketValue(0,0,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>PV to your direction</t>
+          <t>IR DV01  (+1bp rates)</t>
         </is>
       </c>
       <c r="B23" s="44">
-        <f>IF(B9="Buy protection",B13-B14,B14-B13)</f>
-        <v/>
-      </c>
-      <c r="J23" s="139" t="inlineStr">
-        <is>
-          <t>interest enters with a + sign, which the wording alone does not settle.</t>
-        </is>
+        <f>IF(OR($O$22="",$O$24=""),"",$O$24-$O$22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="177" t="inlineStr">
+        <is>
+          <t>IR DV01: parallel +1bp on the discount curve, curve re-stripped.</t>
+        </is>
+      </c>
+      <c r="N23" s="126" t="inlineStr">
+        <is>
+          <t>MV  spreads +1bp</t>
+        </is>
+      </c>
+      <c r="O23" s="229">
+        <f>IFERROR(CDS_MarketValue(1,0,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Upfront (% notional)</t>
-        </is>
-      </c>
-      <c r="B24" s="60">
-        <f>B17/B4*100</f>
+          <t>Rec01  (+1% recovery)</t>
+        </is>
+      </c>
+      <c r="B24" s="44">
+        <f>IF(OR($O$22="",$O$25=""),"",$O$25-$O$22)</f>
+        <v/>
+      </c>
+      <c r="C24" s="177" t="inlineStr">
+        <is>
+          <t>Rec01: recovery +1%, hazards re-fitted so the quotes still reprice.</t>
+        </is>
+      </c>
+      <c r="N24" s="126" t="inlineStr">
+        <is>
+          <t>MV  rates +1bp</t>
+        </is>
+      </c>
+      <c r="O24" s="229">
+        <f>IFERROR(CDS_MarketValue(0,1,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="132" t="inlineStr">
-        <is>
-          <t>PV01  (premium leg net of AI, per 1bp)</t>
-        </is>
-      </c>
-      <c r="B25" s="120">
-        <f>B4*(B12-CDS_Parameters!$B$26)*0.0001</f>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Jump-to-default (immediate)</t>
+        </is>
+      </c>
+      <c r="B25" s="45">
+        <f>IF(B9="Buy protection",B4*(1-B5),-B4*(1-B5))-B17</f>
+        <v/>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Default-now P&amp;L to your direction: LGD payout - current PV.</t>
+        </is>
+      </c>
+      <c r="N25" s="126" t="inlineStr">
+        <is>
+          <t>MV  recovery +1%</t>
+        </is>
+      </c>
+      <c r="O25" s="229">
+        <f>IFERROR(CDS_MarketValue(0,0,0.01,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="94" t="inlineStr">
         <is>
-          <t>Market Value  (3.1)</t>
-        </is>
-      </c>
-      <c r="B26" s="119">
-        <f>B13-B14</f>
-        <v/>
-      </c>
-      <c r="C26" s="65" t="inlineStr">
-        <is>
-          <t>Protection leg minus premium leg, both to the pricing date.</t>
+          <t>Accrued Interest  A*C*D0</t>
+        </is>
+      </c>
+      <c r="B26" s="120">
+        <f>B4*(B6/10000)*CDS_Parameters!$B$25</f>
+        <v/>
+      </c>
+      <c r="N26" s="177" t="inlineStr">
+        <is>
+          <t>Each measure is a difference of two full valuations. Holding hazards fixed and multiplying RPV01 by a bump answers a different question - that is what made Rec01 come out with the wrong sign.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67" t="inlineStr">
         <is>
-          <t>RISK MEASURES (full revalue, curve re-stripped on each bump)</t>
-        </is>
-      </c>
-      <c r="N27" s="67" t="inlineStr">
-        <is>
-          <t>full-revalue working</t>
+          <t>Upfront  (3.2)</t>
+        </is>
+      </c>
+      <c r="B27" s="119">
+        <f>B20/CDS_Parameters!$B$22+B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="65" t="inlineStr">
+        <is>
+          <t>Market Value / D(T_s) + Accrued Interest. Identically zero when C = S.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>CS01 / Spread DV01  (+1bp)</t>
-        </is>
-      </c>
-      <c r="B28" s="44">
-        <f>IF(OR($O$22="",$O$23=""),"",$O$23-$O$22)</f>
-        <v/>
-      </c>
-      <c r="C28" s="177" t="inlineStr">
-        <is>
-          <t>Spread DV01: revalue at +1bp on every quote, curve re-stripped (p.9).</t>
-        </is>
-      </c>
-      <c r="N28" s="126" t="inlineStr">
-        <is>
-          <t>MV base</t>
-        </is>
-      </c>
-      <c r="O28" s="229">
-        <f>IFERROR(CDS_MarketValue(0,0,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
-        <v/>
+      <c r="A28" s="67" t="inlineStr">
+        <is>
+          <t>CDSW SCREEN OUTPUT</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>IR DV01  (+1bp rates)</t>
-        </is>
-      </c>
-      <c r="B29" s="44">
-        <f>IF(OR($O$22="",$O$24=""),"",$O$24-$O$22)</f>
-        <v/>
-      </c>
-      <c r="C29" s="177" t="inlineStr">
-        <is>
-          <t>IR DV01: parallel +1bp on the discount curve, curve re-stripped.</t>
-        </is>
-      </c>
-      <c r="N29" s="126" t="inlineStr">
-        <is>
-          <t>MV  spreads +1bp</t>
-        </is>
-      </c>
-      <c r="O29" s="229">
-        <f>IFERROR(CDS_MarketValue(1,0,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
-        <v/>
+      <c r="A29" s="65" t="inlineStr">
+        <is>
+          <t>Settlement figures in CDSW order. S = par spread from the curve (B15), C = contractual coupon (B6).</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Rec01  (+1% recovery)</t>
-        </is>
-      </c>
-      <c r="B30" s="44">
-        <f>IF(OR($O$22="",$O$25=""),"",$O$25-$O$22)</f>
-        <v/>
-      </c>
-      <c r="C30" s="177" t="inlineStr">
-        <is>
-          <t>Rec01: recovery +1%, hazards re-fitted so the quotes still reprice.</t>
-        </is>
-      </c>
-      <c r="N30" s="126" t="inlineStr">
-        <is>
-          <t>MV  rates +1bp</t>
-        </is>
-      </c>
-      <c r="O30" s="229">
-        <f>IFERROR(CDS_MarketValue(0,1,0,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
-        <v/>
+      <c r="A30" s="94" t="inlineStr">
+        <is>
+          <t>1st accrual start</t>
+        </is>
+      </c>
+      <c r="B30" s="86">
+        <f>IF(MONTH((EDATE(CDS_Parameters!$B$5,-3)+IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=6,2,IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=7,1,0))))&lt;&gt;MONTH(EDATE(CDS_Parameters!$B$5,-3)),(EDATE(CDS_Parameters!$B$5,-3)-IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=6,1,IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=7,2,0))),(EDATE(CDS_Parameters!$B$5,-3)+IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=6,2,IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=7,1,0))))</f>
+        <v/>
+      </c>
+      <c r="C30" s="65" t="inlineStr">
+        <is>
+          <t>Previous IMM roll, business-day adjusted. 20 Jun 2026 is a Saturday, so the screen shows 06/22/26.</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Jump-to-default (immediate)</t>
-        </is>
-      </c>
-      <c r="B31" s="45">
-        <f>IF(B9="Buy protection",B4*(1-B5),-B4*(1-B5))-B17</f>
-        <v/>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Default-now P&amp;L to your direction: LGD payout - current PV.</t>
-        </is>
-      </c>
-      <c r="N31" s="126" t="inlineStr">
-        <is>
-          <t>MV  recovery +1%</t>
-        </is>
-      </c>
-      <c r="O31" s="229">
-        <f>IFERROR(CDS_MarketValue(0,0,0.01,Hazard_Bootstrap!$B$7:$B$12,Hazard_Bootstrap!$C$7:$C$12,CDS_Parameters!$B$8,CDS_Parameters!$B$26,CDS_Schedule!$C$7:$C$46,CDS_Schedule!$D$7:$D$46,CDS_Schedule!$E$7:$E$46,CDS_Schedule!$F$7:$F$46,CDS_Schedule!$G$7:$G$46,CDS_Schedule!$H$7:$H$46,$B$4,$B$6,$B$8),"")</f>
-        <v/>
+      <c r="A31" s="67" t="inlineStr">
+        <is>
+          <t>Points upfront</t>
+        </is>
+      </c>
+      <c r="B31" s="71">
+        <f>(($B$15/10000)-CDS_Parameters!$B$10/10000)*$B$12*100</f>
+        <v/>
+      </c>
+      <c r="C31" s="65" t="inlineStr">
+        <is>
+          <t>(S - C) * RPV01 * 100, protection buyer.</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="94" t="inlineStr">
-        <is>
-          <t>Accrued Interest  A*C*D0</t>
-        </is>
-      </c>
-      <c r="B32" s="120">
-        <f>B4*(B6/10000)*CDS_Parameters!$B$25</f>
-        <v/>
-      </c>
-      <c r="N32" s="177" t="inlineStr">
-        <is>
-          <t>Each measure is a difference of two full valuations. Holding hazards fixed and multiplying RPV01 by a bump answers a different question - that is what made Rec01 come out with the wrong sign.</t>
+      <c r="A32" s="67" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B32" s="71">
+        <f>100-B31</f>
+        <v/>
+      </c>
+      <c r="C32" s="65" t="inlineStr">
+        <is>
+          <t>100 - points upfront.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="67" t="inlineStr">
-        <is>
-          <t>Upfront  (3.2)</t>
-        </is>
-      </c>
-      <c r="B33" s="119">
-        <f>B20/CDS_Parameters!$B$22+B26</f>
+      <c r="A33" s="94" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="B33" s="103">
+        <f>IF(CDS_Parameters!$B$15="Buy protection",1,-1)*(($B$15/10000)-CDS_Parameters!$B$10/10000)*$B$12*CDS_Parameters!$B$9</f>
         <v/>
       </c>
       <c r="C33" s="65" t="inlineStr">
         <is>
-          <t>Market Value / D(T_s) + Accrued Interest. Identically zero when C = S.</t>
+          <t>Clean upfront in cash.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="67" t="inlineStr">
-        <is>
-          <t>CDSW SCREEN OUTPUT</t>
+      <c r="A34" s="94" t="inlineStr">
+        <is>
+          <t>Accrued days</t>
+        </is>
+      </c>
+      <c r="B34" s="104">
+        <f>MAX(0,CDS_Parameters!$B$4-B30+1)</f>
+        <v/>
+      </c>
+      <c r="C34" s="65" t="inlineStr">
+        <is>
+          <t>ISDA counts both endpoints.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="65" t="inlineStr">
-        <is>
-          <t>Settlement figures in CDSW order. S = par spread from the curve (B15), C = contractual coupon (B6).</t>
+      <c r="A35" s="94" t="inlineStr">
+        <is>
+          <t>Accrued</t>
+        </is>
+      </c>
+      <c r="B35" s="103">
+        <f>-IF(CDS_Parameters!$B$15="Buy protection",1,-1)*CDS_Parameters!$B$10/10000*CDS_Parameters!$B$9*B34/360</f>
+        <v/>
+      </c>
+      <c r="C35" s="65" t="inlineStr">
+        <is>
+          <t>Coupon * notional * days/360.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="94" t="inlineStr">
-        <is>
-          <t>1st accrual start</t>
-        </is>
-      </c>
-      <c r="B36" s="86">
-        <f>IF(MONTH((EDATE(CDS_Parameters!$B$5,-3)+IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=6,2,IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=7,1,0))))&lt;&gt;MONTH(EDATE(CDS_Parameters!$B$5,-3)),(EDATE(CDS_Parameters!$B$5,-3)-IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=6,1,IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=7,2,0))),(EDATE(CDS_Parameters!$B$5,-3)+IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=6,2,IF(WEEKDAY(EDATE(CDS_Parameters!$B$5,-3),2)=7,1,0))))</f>
+      <c r="A36" s="67" t="inlineStr">
+        <is>
+          <t>Cash Amount</t>
+        </is>
+      </c>
+      <c r="B36" s="105">
+        <f>B33+B35</f>
         <v/>
       </c>
       <c r="C36" s="65" t="inlineStr">
         <is>
-          <t>Previous IMM roll, business-day adjusted. 20 Jun 2026 is a Saturday, so the screen shows 06/22/26.</t>
+          <t>Principal + accrued.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="67" t="inlineStr">
+      <c r="A37" s="94" t="inlineStr">
+        <is>
+          <t>Default Exposure</t>
+        </is>
+      </c>
+      <c r="B37" s="103">
+        <f>(1-CDS_Parameters!$B$8)*CDS_Parameters!$B$9-B33</f>
+        <v/>
+      </c>
+      <c r="C37" s="65" t="inlineStr">
+        <is>
+          <t>(1-R) * notional less the principal already paid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="66" t="inlineStr">
+        <is>
+          <t>Upfront (3.2) above is the paper's total. How it splits into CDSW's Principal / Accrued / Cash is INFERRED, not confirmed by the paper. A capture with non-zero accrued would settle it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="65" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="67" t="inlineStr">
+        <is>
+          <t>MODEL vs CAPTURED CDSW  (active entity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="177" t="inlineStr">
+        <is>
+          <t>Blank until a CDSW capture is typed into CDS_Entities O:AC for the live name. A zero there reads as no capture, not as a captured zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="141" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B43" s="141" t="inlineStr">
+        <is>
+          <t>CDSW captured</t>
+        </is>
+      </c>
+      <c r="C43" s="141" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D43" s="141" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="94" t="inlineStr">
         <is>
           <t>Points upfront</t>
         </is>
       </c>
-      <c r="B37" s="71">
-        <f>(($B$15/10000)-CDS_Parameters!$B$10/10000)*$B$12*100</f>
-        <v/>
-      </c>
-      <c r="C37" s="65" t="inlineStr">
-        <is>
-          <t>(S - C) * RPV01 * 100, protection buyer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="B44" s="87">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$S$5:$S$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$S$5:$S$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="93">
+        <f>B31</f>
+        <v/>
+      </c>
+      <c r="D44" s="93">
+        <f>IF(OR(B44="",NOT(ISNUMBER(B44)),NOT(ISNUMBER(C44))),"",C44-B44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="94" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="B38" s="71">
-        <f>100-B31</f>
-        <v/>
-      </c>
-      <c r="C38" s="65" t="inlineStr">
-        <is>
-          <t>100 - points upfront.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="94" t="inlineStr">
+      <c r="B45" s="87">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$T$5:$T$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$T$5:$T$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="93">
+        <f>B32</f>
+        <v/>
+      </c>
+      <c r="D45" s="93">
+        <f>IF(OR(B45="",NOT(ISNUMBER(B45)),NOT(ISNUMBER(C45))),"",C45-B45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="94" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="B39" s="103">
-        <f>IF(CDS_Parameters!$B$15="Buy protection",1,-1)*(($B$15/10000)-CDS_Parameters!$B$10/10000)*$B$12*CDS_Parameters!$B$9</f>
-        <v/>
-      </c>
-      <c r="C39" s="65" t="inlineStr">
-        <is>
-          <t>Clean upfront in cash.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="94" t="inlineStr">
+      <c r="B46" s="87">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$U$5:$U$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$U$5:$U$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="93">
+        <f>B33</f>
+        <v/>
+      </c>
+      <c r="D46" s="93">
+        <f>IF(OR(B46="",NOT(ISNUMBER(B46)),NOT(ISNUMBER(C46))),"",C46-B46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="94" t="inlineStr">
         <is>
           <t>Accrued days</t>
         </is>
       </c>
-      <c r="B40" s="104">
-        <f>MAX(0,CDS_Parameters!$B$4-B30+1)</f>
-        <v/>
-      </c>
-      <c r="C40" s="65" t="inlineStr">
-        <is>
-          <t>ISDA counts both endpoints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="94" t="inlineStr">
+      <c r="B47" s="87">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$V$5:$V$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$V$5:$V$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="93">
+        <f>B34</f>
+        <v/>
+      </c>
+      <c r="D47" s="93">
+        <f>IF(OR(B47="",NOT(ISNUMBER(B47)),NOT(ISNUMBER(C47))),"",C47-B47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="94" t="inlineStr">
         <is>
           <t>Accrued</t>
         </is>
       </c>
-      <c r="B41" s="103">
-        <f>-IF(CDS_Parameters!$B$15="Buy protection",1,-1)*CDS_Parameters!$B$10/10000*CDS_Parameters!$B$9*B34/360</f>
-        <v/>
-      </c>
-      <c r="C41" s="65" t="inlineStr">
-        <is>
-          <t>Coupon * notional * days/360.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="67" t="inlineStr">
-        <is>
-          <t>Cash Amount</t>
-        </is>
-      </c>
-      <c r="B42" s="105">
-        <f>B33+B35</f>
-        <v/>
-      </c>
-      <c r="C42" s="65" t="inlineStr">
-        <is>
-          <t>Principal + accrued.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="94" t="inlineStr">
-        <is>
-          <t>Default Exposure</t>
-        </is>
-      </c>
-      <c r="B43" s="103">
-        <f>(1-CDS_Parameters!$B$8)*CDS_Parameters!$B$9-B33</f>
-        <v/>
-      </c>
-      <c r="C43" s="65" t="inlineStr">
-        <is>
-          <t>(1-R) * notional less the principal already paid.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="66" t="inlineStr">
-        <is>
-          <t>Upfront (3.2) above is the paper's total. How it splits into CDSW's Principal / Accrued / Cash is INFERRED, not confirmed by the paper. A capture with non-zero accrued would settle it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="65" t="n"/>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="67" t="inlineStr">
-        <is>
-          <t>MODEL vs CAPTURED CDSW  (active entity)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="177" t="inlineStr">
-        <is>
-          <t>Blank until a CDSW capture is typed into CDS_Entities O:AC for the live name. A zero there reads as no capture, not as a captured zero.</t>
-        </is>
+      <c r="B48" s="87">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$W$5:$W$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$W$5:$W$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="93">
+        <f>B35</f>
+        <v/>
+      </c>
+      <c r="D48" s="93">
+        <f>IF(OR(B48="",NOT(ISNUMBER(B48)),NOT(ISNUMBER(C48))),"",C48-B48)</f>
+        <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="141" t="inlineStr">
-        <is>
-          <t>Measure</t>
-        </is>
-      </c>
-      <c r="B49" s="141" t="inlineStr">
-        <is>
-          <t>CDSW captured</t>
-        </is>
-      </c>
-      <c r="C49" s="141" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="D49" s="141" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="A49" s="94" t="inlineStr">
+        <is>
+          <t>Cash amount</t>
+        </is>
+      </c>
+      <c r="B49" s="87">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$X$5:$X$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$X$5:$X$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="93">
+        <f>B36</f>
+        <v/>
+      </c>
+      <c r="D49" s="93">
+        <f>IF(OR(B49="",NOT(ISNUMBER(B49)),NOT(ISNUMBER(C49))),"",C49-B49)</f>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="94" t="inlineStr">
         <is>
-          <t>Points upfront</t>
+          <t>Def exposure</t>
         </is>
       </c>
       <c r="B50" s="87">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$S$5:$S$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$S$5:$S$14,CDS_Parameters!$B$28)),"")</f>
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$AB$5:$AB$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$AB$5:$AB$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
       <c r="C50" s="93">
-        <f>B31</f>
+        <f>B37</f>
         <v/>
       </c>
       <c r="D50" s="93">
-        <f>IF(OR(B44="",NOT(ISNUMBER(B44)),NOT(ISNUMBER(C44))),"",C44-B44)</f>
+        <f>IF(OR(B50="",NOT(ISNUMBER(B50)),NOT(ISNUMBER(C50))),"",C50-B50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="94" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="B51" s="87">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$T$5:$T$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$T$5:$T$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="93">
-        <f>B32</f>
-        <v/>
-      </c>
-      <c r="D51" s="93">
-        <f>IF(OR(B45="",NOT(ISNUMBER(B45)),NOT(ISNUMBER(C45))),"",C45-B45)</f>
+      <c r="A51" s="190" t="inlineStr">
+        <is>
+          <t>Spread DV01</t>
+        </is>
+      </c>
+      <c r="B51" s="180">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$Y$5:$Y$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$Y$5:$Y$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="180">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="D51" s="180">
+        <f>IF(OR(B51="",NOT(ISNUMBER(B51)),NOT(ISNUMBER(C51))),"",C51-B51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="94" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="B52" s="87">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$U$5:$U$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$U$5:$U$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="93">
-        <f>B33</f>
-        <v/>
-      </c>
-      <c r="D52" s="93">
-        <f>IF(OR(B46="",NOT(ISNUMBER(B46)),NOT(ISNUMBER(C46))),"",C46-B46)</f>
+      <c r="A52" s="190" t="inlineStr">
+        <is>
+          <t>IR DV01</t>
+        </is>
+      </c>
+      <c r="B52" s="180">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$Z$5:$Z$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$Z$5:$Z$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="180">
+        <f>B23</f>
+        <v/>
+      </c>
+      <c r="D52" s="180">
+        <f>IF(OR(B52="",NOT(ISNUMBER(B52)),NOT(ISNUMBER(C52))),"",C52-B52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="94" t="inlineStr">
-        <is>
-          <t>Accrued days</t>
-        </is>
-      </c>
-      <c r="B53" s="87">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$V$5:$V$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$V$5:$V$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="93">
-        <f>B34</f>
-        <v/>
-      </c>
-      <c r="D53" s="93">
-        <f>IF(OR(B47="",NOT(ISNUMBER(B47)),NOT(ISNUMBER(C47))),"",C47-B47)</f>
+      <c r="A53" s="190" t="inlineStr">
+        <is>
+          <t>Rec risk 1%</t>
+        </is>
+      </c>
+      <c r="B53" s="180">
+        <f>IFERROR(IF(N(INDEX(CDS_Entities!$AA$5:$AA$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$AA$5:$AA$14,CDS_Parameters!$B$28)),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="180">
+        <f>B24</f>
+        <v/>
+      </c>
+      <c r="D53" s="180">
+        <f>IF(OR(B53="",NOT(ISNUMBER(B53)),NOT(ISNUMBER(C53))),"",C53-B53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="94" t="inlineStr">
-        <is>
-          <t>Accrued</t>
-        </is>
-      </c>
-      <c r="B54" s="87">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$W$5:$W$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$W$5:$W$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="93">
-        <f>B35</f>
-        <v/>
-      </c>
-      <c r="D54" s="93">
-        <f>IF(OR(B48="",NOT(ISNUMBER(B48)),NOT(ISNUMBER(C48))),"",C48-B48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="94" t="inlineStr">
-        <is>
-          <t>Cash amount</t>
-        </is>
-      </c>
-      <c r="B55" s="87">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$X$5:$X$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$X$5:$X$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="93">
-        <f>B36</f>
-        <v/>
-      </c>
-      <c r="D55" s="93">
-        <f>IF(OR(B49="",NOT(ISNUMBER(B49)),NOT(ISNUMBER(C49))),"",C49-B49)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="94" t="inlineStr">
-        <is>
-          <t>Def exposure</t>
-        </is>
-      </c>
-      <c r="B56" s="87">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$AB$5:$AB$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$AB$5:$AB$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C56" s="93">
-        <f>B37</f>
-        <v/>
-      </c>
-      <c r="D56" s="93">
-        <f>IF(OR(B50="",NOT(ISNUMBER(B50)),NOT(ISNUMBER(C50))),"",C50-B50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="190" t="inlineStr">
-        <is>
-          <t>Spread DV01</t>
-        </is>
-      </c>
-      <c r="B57" s="180">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$Y$5:$Y$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$Y$5:$Y$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="180">
-        <f>B22</f>
-        <v/>
-      </c>
-      <c r="D57" s="180">
-        <f>IF(OR(B51="",NOT(ISNUMBER(B51)),NOT(ISNUMBER(C51))),"",C51-B51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="190" t="inlineStr">
-        <is>
-          <t>IR DV01</t>
-        </is>
-      </c>
-      <c r="B58" s="180">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$Z$5:$Z$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$Z$5:$Z$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C58" s="180">
-        <f>B23</f>
-        <v/>
-      </c>
-      <c r="D58" s="180">
-        <f>IF(OR(B52="",NOT(ISNUMBER(B52)),NOT(ISNUMBER(C52))),"",C52-B52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="190" t="inlineStr">
-        <is>
-          <t>Rec risk 1%</t>
-        </is>
-      </c>
-      <c r="B59" s="180">
-        <f>IFERROR(IF(N(INDEX(CDS_Entities!$AA$5:$AA$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$AA$5:$AA$14,CDS_Parameters!$B$28)),"")</f>
-        <v/>
-      </c>
-      <c r="C59" s="180">
-        <f>B24</f>
-        <v/>
-      </c>
-      <c r="D59" s="180">
-        <f>IF(OR(B53="",NOT(ISNUMBER(B53)),NOT(ISNUMBER(C53))),"",C53-B53)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="190" t="inlineStr">
+      <c r="A54" s="190" t="inlineStr">
         <is>
           <t>Prob 5Y (1-Q)</t>
         </is>
       </c>
-      <c r="B60" s="180">
+      <c r="B54" s="180">
         <f>IFERROR(IF(N(INDEX(CDS_Entities!$AC$5:$AC$14,CDS_Parameters!$B$28))=0,"",INDEX(CDS_Entities!$AC$5:$AC$14,CDS_Parameters!$B$28)),"")</f>
         <v/>
       </c>
-      <c r="C60" s="180">
+      <c r="C54" s="180">
         <f>IFERROR(INDEX(Hazard_Bootstrap!$F$7:$F$12,MATCH(5,CDS_Quotes!$B$7:$B$12,0)),"")</f>
         <v/>
       </c>
-      <c r="D60" s="180">
+      <c r="D54" s="180">
         <f>IF(OR(B54="",NOT(ISNUMBER(B54)),NOT(ISNUMBER(C54))),"",C54-B54)</f>
         <v/>
       </c>

--- a/bloomberg/CDS_PricerSheet_v7.xlsx
+++ b/bloomberg/CDS_PricerSheet_v7.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="175" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="176" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -235,6 +235,12 @@
       <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="13">
@@ -327,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -654,6 +660,7 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1086,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1115,14 +1122,14 @@
     <row r="5">
       <c r="A5" s="233" t="inlineStr">
         <is>
-          <t>1.  Open both workbooks and keep both open.</t>
+          <t>1.  Open both workbooks, keep both open.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="233" t="inlineStr">
         <is>
-          <t>2.  Right-click the CDS_Pricer_NEW tab &gt; Move or Copy &gt; To book: your CDS_Pricer workbook.</t>
+          <t>2.  Right-click CDS_Pricer_NEW &gt; Move or Copy &gt; To book: your CDS_Pricer workbook.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1157,7 @@
     <row r="10">
       <c r="A10" s="233" t="inlineStr">
         <is>
-          <t>4.  Delete the old CDS_Pricer tab, then rename this one to exactly  CDS_Pricer</t>
+          <t>4.  Delete the old CDS_Pricer, rename this one to exactly  CDS_Pricer</t>
         </is>
       </c>
     </row>
@@ -1158,23 +1165,23 @@
       <c r="A11" s="231" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="232" t="inlineStr">
-        <is>
-          <t>Modules needed: CDSStrip.bas and CDSRisk.bas. Save as .xlsm.</t>
+      <c r="A12" s="234" t="inlineStr">
+        <is>
+          <t>ALSO CHANGE, on CDS_Schedule:   B7  =CDS_Parameters!$B$23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="231" t="inlineStr">
         <is>
-          <t>Sheets it reads: CDS_Parameters, CDS_Schedule, Curve_Interface, Hazard_Bootstrap,</t>
+          <t>It currently reads =VAL_DATE. Period 1 must accrue from the 1st accrual start,</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="231" t="inlineStr">
         <is>
-          <t>CDS_Quotes, CDS_Entities, Steps. All are in your workbook already.</t>
+          <t>not the valuation date, or the premium leg is short and principal is ~4,100 out on 10mm.</t>
         </is>
       </c>
     </row>
@@ -1182,9 +1189,23 @@
       <c r="A15" s="231" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="231" t="inlineStr">
-        <is>
-          <t>Opened on its own the tab shows #REF - expected, those sheets are not in this file.</t>
+      <c r="A16" s="232" t="inlineStr">
+        <is>
+          <t>Modules: CDSStrip.bas and CDSRisk.bas. Save as .xlsm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="165" t="inlineStr">
+        <is>
+          <t>To match a CDSW screen, put the traded spread at ALL SIX tenors on Entities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="231" t="inlineStr">
+        <is>
+          <t>A CDSW Term table with one row means it is pricing flat at that spread.</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1691,12 @@
         </is>
       </c>
       <c r="B31" s="71">
-        <f>(($B$15/10000)-CDS_Parameters!$B$10/10000)*$B$12*100</f>
-        <v/>
-      </c>
-      <c r="C31" s="65" t="inlineStr">
-        <is>
-          <t>(S - C) * RPV01 * 100, protection buyer.</t>
+        <f>IF($B$27="","",IF($B$9="Buy protection",1,-1)*$B$27/$B$4*100)</f>
+        <v/>
+      </c>
+      <c r="C31" s="177" t="inlineStr">
+        <is>
+          <t>Principal / notional. From (3.2), not (S-C)*RPV01.</t>
         </is>
       </c>
     </row>
@@ -1686,10 +1707,10 @@
         </is>
       </c>
       <c r="B32" s="71">
-        <f>100-B31</f>
-        <v/>
-      </c>
-      <c r="C32" s="65" t="inlineStr">
+        <f>IF($B$31="","",100-$B$31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="177" t="inlineStr">
         <is>
           <t>100 - points upfront.</t>
         </is>
@@ -1702,12 +1723,12 @@
         </is>
       </c>
       <c r="B33" s="103">
-        <f>IF(CDS_Parameters!$B$15="Buy protection",1,-1)*(($B$15/10000)-CDS_Parameters!$B$10/10000)*$B$12*CDS_Parameters!$B$9</f>
-        <v/>
-      </c>
-      <c r="C33" s="65" t="inlineStr">
-        <is>
-          <t>Clean upfront in cash.</t>
+        <f>IF($B$27="","",IF($B$9="Buy protection",1,-1)*$B$27)</f>
+        <v/>
+      </c>
+      <c r="C33" s="177" t="inlineStr">
+        <is>
+          <t>Upfront (3.2) = Market Value / D(T_s) + Accrued Interest.</t>
         </is>
       </c>
     </row>
@@ -1750,10 +1771,10 @@
         </is>
       </c>
       <c r="B36" s="105">
-        <f>B33+B35</f>
-        <v/>
-      </c>
-      <c r="C36" s="65" t="inlineStr">
+        <f>IF(OR($B$33="",$B$35=""),"",$B$33+$B$35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="177" t="inlineStr">
         <is>
           <t>Principal + accrued.</t>
         </is>
@@ -1766,19 +1787,19 @@
         </is>
       </c>
       <c r="B37" s="103">
-        <f>(1-CDS_Parameters!$B$8)*CDS_Parameters!$B$9-B33</f>
-        <v/>
-      </c>
-      <c r="C37" s="65" t="inlineStr">
+        <f>IF($B$33="","",(1-$B$5)*$B$4-$B$33)</f>
+        <v/>
+      </c>
+      <c r="C37" s="177" t="inlineStr">
         <is>
           <t>(1-R) * notional less the principal already paid.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="66" t="inlineStr">
-        <is>
-          <t>Upfront (3.2) above is the paper's total. How it splits into CDSW's Principal / Accrued / Cash is INFERRED, not confirmed by the paper. A capture with non-zero accrued would settle it.</t>
+      <c r="A38" s="177" t="inlineStr">
+        <is>
+          <t>CDSW order. Principal is (3.2) end to end: Market Value / D(T_s) + Accrued Interest, compounded to settlement three business days on. The (S-C)*RPV01 shortcut drops the -S*AI term and the compounding.</t>
         </is>
       </c>
     </row>

--- a/bloomberg/CDS_PricerSheet_v7.xlsx
+++ b/bloomberg/CDS_PricerSheet_v7.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="175" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="176" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -230,17 +230,6 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="13">
@@ -333,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,8 +648,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1093,16 +1080,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="230" t="inlineStr">
         <is>
-          <t>Moving the reformed CDS_Pricer in</t>
+          <t>Reformed CDS_Pricer</t>
         </is>
       </c>
     </row>
@@ -1112,100 +1099,21 @@
     <row r="3">
       <c r="A3" s="232" t="inlineStr">
         <is>
-          <t>Move the CDS_Pricer_NEW tab only. Leave this sheet behind.</t>
+          <t>Move CDS_Pricer_NEW only. Ctrl+H out [CDS_PricerSheet_v7.xlsx] after the move.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="231" t="inlineStr"/>
+      <c r="A4" s="165" t="inlineStr">
+        <is>
+          <t>Also on CDS_Schedule:  B7 = CDS_Parameters!$B$23</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="233" t="inlineStr">
-        <is>
-          <t>1.  Open both workbooks, keep both open.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="233" t="inlineStr">
-        <is>
-          <t>2.  Right-click CDS_Pricer_NEW &gt; Move or Copy &gt; To book: your CDS_Pricer workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="233" t="inlineStr">
-        <is>
-          <t>3.  On the moved tab: Ctrl+H, Options, Look in Formulas, Within Sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Find what:     [CDS_PricerSheet_v7.xlsx]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Replace with:  (leave empty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="233" t="inlineStr">
-        <is>
-          <t>4.  Delete the old CDS_Pricer, rename this one to exactly  CDS_Pricer</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="231" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="234" t="inlineStr">
-        <is>
-          <t>ALSO CHANGE, on CDS_Schedule:   B7  =CDS_Parameters!$B$23</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="231" t="inlineStr">
-        <is>
-          <t>It currently reads =VAL_DATE. Period 1 must accrue from the 1st accrual start,</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="231" t="inlineStr">
-        <is>
-          <t>not the valuation date, or the premium leg is short and principal is ~4,100 out on 10mm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="231" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="232" t="inlineStr">
-        <is>
-          <t>Modules: CDSStrip.bas and CDSRisk.bas. Save as .xlsm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="165" t="inlineStr">
-        <is>
-          <t>To match a CDSW screen, put the traded spread at ALL SIX tenors on Entities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="231" t="inlineStr">
-        <is>
-          <t>A CDSW Term table with one row means it is pricing flat at that spread.</t>
+      <c r="A5" s="232" t="inlineStr">
+        <is>
+          <t>Modules: CDSStrip.bas and CDSRisk.bas. N20 on the sheet says whether CDSRisk is loaded.</t>
         </is>
       </c>
     </row>
@@ -1509,6 +1417,10 @@
           <t>Protection leg minus premium leg, both to the pricing date.</t>
         </is>
       </c>
+      <c r="N20" s="66">
+        <f>IFERROR(CDS_RiskLoaded(),"CDSRisk.bas NOT imported")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="67" t="inlineStr">
@@ -1651,6 +1563,11 @@
       <c r="C27" s="65" t="inlineStr">
         <is>
           <t>Market Value / D(T_s) + Accrued Interest. Identically zero when C = S.</t>
+        </is>
+      </c>
+      <c r="N27" s="177" t="inlineStr">
+        <is>
+          <t>If N20 says loaded but O22:O25 are blank, the call itself is failing - not the module. Delete the IFERROR wrapper on O22 to see the real error.</t>
         </is>
       </c>
     </row>

--- a/bloomberg/CDS_PricerSheet_v7.xlsx
+++ b/bloomberg/CDS_PricerSheet_v7.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="175" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="176" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -230,6 +230,17 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="13">
@@ -322,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -648,6 +659,8 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1080,10 +1093,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1099,21 +1112,48 @@
     <row r="3">
       <c r="A3" s="232" t="inlineStr">
         <is>
-          <t>Move CDS_Pricer_NEW only. Ctrl+H out [CDS_PricerSheet_v7.xlsx] after the move.</t>
+          <t>Move CDS_Pricer_NEW only. After the move: Ctrl+H, find [CDS_PricerSheet_v7.xlsx], replace with nothing.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="165" t="inlineStr">
-        <is>
-          <t>Also on CDS_Schedule:  B7 = CDS_Parameters!$B$23</t>
+      <c r="A4" s="233" t="inlineStr">
+        <is>
+          <t>Delete the old CDS_Pricer, rename this one to exactly CDS_Pricer.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="232" t="inlineStr">
-        <is>
-          <t>Modules: CDSStrip.bas and CDSRisk.bas. N20 on the sheet says whether CDSRisk is loaded.</t>
+      <c r="A5" s="231" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="234" t="inlineStr">
+        <is>
+          <t>TWO CHANGES ON SHEETS YOU ALREADY HAVE - these do not travel with the tab:</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   CDS_Schedule!B7   =CDS_Parameters!$B$23      (was =VAL_DATE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   CDS_Quotes!F7:F12  override must beat BDP - see the repo, commit notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="231" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="232" t="inlineStr">
+        <is>
+          <t>Modules: CDSStrip.bas and CDSRisk.bas. N20 on the sheet reports whether CDSRisk loaded.</t>
         </is>
       </c>
     </row>

--- a/bloomberg/CDS_PricerSheet_v7.xlsx
+++ b/bloomberg/CDS_PricerSheet_v7.xlsx
@@ -1096,7 +1096,7 @@
   <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="105" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1112,7 +1112,7 @@
     <row r="3">
       <c r="A3" s="232" t="inlineStr">
         <is>
-          <t>Move CDS_Pricer_NEW only. After the move: Ctrl+H, find [CDS_PricerSheet_v7.xlsx], replace with nothing.</t>
+          <t>Move CDS_Pricer_NEW only. Then Ctrl+H: find [CDS_PricerSheet_v7.xlsx], replace with nothing.</t>
         </is>
       </c>
     </row>
@@ -1129,21 +1129,21 @@
     <row r="6">
       <c r="A6" s="234" t="inlineStr">
         <is>
-          <t>TWO CHANGES ON SHEETS YOU ALREADY HAVE - these do not travel with the tab:</t>
+          <t>On sheets you already have (these do not travel with the tab):</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="165" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CDS_Schedule!B7   =CDS_Parameters!$B$23      (was =VAL_DATE)</t>
+          <t xml:space="preserve">   CDS_Schedule!B7    =CDS_Parameters!$B$23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="165" t="inlineStr">
         <is>
-          <t xml:space="preserve">   CDS_Quotes!F7:F12  override must beat BDP - see the repo, commit notes</t>
+          <t xml:space="preserve">   CDS_Quotes!F7:F12  override beats BDP - see repo</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
     <row r="10">
       <c r="A10" s="232" t="inlineStr">
         <is>
-          <t>Modules: CDSStrip.bas and CDSRisk.bas. N20 on the sheet reports whether CDSRisk loaded.</t>
+          <t>Modules: CDSStrip.bas, CDSRisk.bas. N20 reports whether CDSRisk loaded.</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
